--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/147.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/147.xlsx
@@ -426,13 +426,13 @@
         <v>4.015458454491085</v>
       </c>
       <c r="E2">
-        <v>-21.63898001528384</v>
+        <v>-27.68126401355629</v>
       </c>
       <c r="F2">
-        <v>-0.9283978841394704</v>
+        <v>-2.959814034800934</v>
       </c>
       <c r="G2">
-        <v>-12.57748535328713</v>
+        <v>-15.56877015711486</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.20074087893335</v>
       </c>
       <c r="E3">
-        <v>-21.69978383578483</v>
+        <v>-27.87760506110686</v>
       </c>
       <c r="F3">
-        <v>-0.8222732510646173</v>
+        <v>-2.793217752954315</v>
       </c>
       <c r="G3">
-        <v>-12.78826778777253</v>
+        <v>-14.80869538566251</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.446327309484296</v>
       </c>
       <c r="E4">
-        <v>-21.61012910738097</v>
+        <v>-27.70524681190092</v>
       </c>
       <c r="F4">
-        <v>-0.7157510016364206</v>
+        <v>-2.869877357511589</v>
       </c>
       <c r="G4">
-        <v>-12.42444545409771</v>
+        <v>-15.06514514058938</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>4.743124794904123</v>
       </c>
       <c r="E5">
-        <v>-22.44737149581509</v>
+        <v>-28.71185865669592</v>
       </c>
       <c r="F5">
-        <v>-0.8149148634255494</v>
+        <v>-2.858493104294916</v>
       </c>
       <c r="G5">
-        <v>-12.40098361786089</v>
+        <v>-14.85167454312609</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>5.09357601018514</v>
       </c>
       <c r="E6">
-        <v>-22.62293590461847</v>
+        <v>-28.98658306084525</v>
       </c>
       <c r="F6">
-        <v>-0.874254962325092</v>
+        <v>-2.856309527821136</v>
       </c>
       <c r="G6">
-        <v>-11.80809801723281</v>
+        <v>-14.88776114477692</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>5.494353671028682</v>
       </c>
       <c r="E7">
-        <v>-23.05141105827622</v>
+        <v>-29.4465243161453</v>
       </c>
       <c r="F7">
-        <v>-0.8995508177043805</v>
+        <v>-2.88152420319495</v>
       </c>
       <c r="G7">
-        <v>-11.40466500618061</v>
+        <v>-14.48760557380859</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>5.944377660463967</v>
       </c>
       <c r="E8">
-        <v>-22.96609913644572</v>
+        <v>-29.11014247414454</v>
       </c>
       <c r="F8">
-        <v>-0.8542349789342335</v>
+        <v>-2.719764758613277</v>
       </c>
       <c r="G8">
-        <v>-11.31380046276423</v>
+        <v>-13.97871678987567</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>6.439376609342314</v>
       </c>
       <c r="E9">
-        <v>-24.10420428100145</v>
+        <v>-30.03326284366013</v>
       </c>
       <c r="F9">
-        <v>-0.5534928798782618</v>
+        <v>-2.836274633817027</v>
       </c>
       <c r="G9">
-        <v>-11.07602383995162</v>
+        <v>-14.00783469316633</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>6.972403744201058</v>
       </c>
       <c r="E10">
-        <v>-24.44388058784279</v>
+        <v>-30.48853297802127</v>
       </c>
       <c r="F10">
-        <v>-0.6485438975124911</v>
+        <v>-2.735645390092346</v>
       </c>
       <c r="G10">
-        <v>-10.62037359410849</v>
+        <v>-13.72408949026817</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>7.541187816311374</v>
       </c>
       <c r="E11">
-        <v>-25.38201284869381</v>
+        <v>-30.94630962274565</v>
       </c>
       <c r="F11">
-        <v>-0.6934240150287655</v>
+        <v>-2.816788947400975</v>
       </c>
       <c r="G11">
-        <v>-10.55564249717912</v>
+        <v>-13.58140994334389</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>8.138880009268355</v>
       </c>
       <c r="E12">
-        <v>-24.93157006762485</v>
+        <v>-31.36030498076388</v>
       </c>
       <c r="F12">
-        <v>-0.6518060083447156</v>
+        <v>-2.683898106806864</v>
       </c>
       <c r="G12">
-        <v>-10.25505158330438</v>
+        <v>-13.43913097242987</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>8.753989218564422</v>
       </c>
       <c r="E13">
-        <v>-26.36112779931424</v>
+        <v>-31.61238248640085</v>
       </c>
       <c r="F13">
-        <v>-0.4593895145528352</v>
+        <v>-2.685992219601141</v>
       </c>
       <c r="G13">
-        <v>-9.966150205728797</v>
+        <v>-13.06558887705174</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>9.373855303524426</v>
       </c>
       <c r="E14">
-        <v>-26.87293140318714</v>
+        <v>-32.80606106397871</v>
       </c>
       <c r="F14">
-        <v>-0.304917218013589</v>
+        <v>-2.670622690809599</v>
       </c>
       <c r="G14">
-        <v>-9.286630938883533</v>
+        <v>-12.77936242027189</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>9.980837479666034</v>
       </c>
       <c r="E15">
-        <v>-27.88910285661234</v>
+        <v>-33.23873637727858</v>
       </c>
       <c r="F15">
-        <v>-0.05164388460764013</v>
+        <v>-2.566412414802616</v>
       </c>
       <c r="G15">
-        <v>-9.243852069425071</v>
+        <v>-12.29426818240248</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>10.55553346615712</v>
       </c>
       <c r="E16">
-        <v>-28.07027804471121</v>
+        <v>-33.64358195356431</v>
       </c>
       <c r="F16">
-        <v>-0.06057120010761041</v>
+        <v>-2.315333426646683</v>
       </c>
       <c r="G16">
-        <v>-8.927115624955299</v>
+        <v>-12.3049413812211</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>11.07908724717763</v>
       </c>
       <c r="E17">
-        <v>-29.09244972619657</v>
+        <v>-34.33176056308795</v>
       </c>
       <c r="F17">
-        <v>0.08378258860643985</v>
+        <v>-2.294608502596042</v>
       </c>
       <c r="G17">
-        <v>-8.273772841689052</v>
+        <v>-12.23354615612117</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>11.53234125574543</v>
       </c>
       <c r="E18">
-        <v>-30.02488516674594</v>
+        <v>-34.59492377309569</v>
       </c>
       <c r="F18">
-        <v>0.1845485129525829</v>
+        <v>-2.185012181736056</v>
       </c>
       <c r="G18">
-        <v>-8.086442311803852</v>
+        <v>-11.78383833952103</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>11.90589227324347</v>
       </c>
       <c r="E19">
-        <v>-30.43073380002436</v>
+        <v>-35.37785164428183</v>
       </c>
       <c r="F19">
-        <v>0.2732186164830476</v>
+        <v>-2.004779315704551</v>
       </c>
       <c r="G19">
-        <v>-7.693308407924321</v>
+        <v>-11.80846879833321</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>12.19546419612002</v>
       </c>
       <c r="E20">
-        <v>-31.03864747199905</v>
+        <v>-36.36895120136355</v>
       </c>
       <c r="F20">
-        <v>0.4038148793714036</v>
+        <v>-1.922719584048426</v>
       </c>
       <c r="G20">
-        <v>-7.4824564519826</v>
+        <v>-11.688070878161</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>12.39955378010366</v>
       </c>
       <c r="E21">
-        <v>-32.12627824526529</v>
+        <v>-37.00382967181692</v>
       </c>
       <c r="F21">
-        <v>0.56345950197373</v>
+        <v>-1.658568129908914</v>
       </c>
       <c r="G21">
-        <v>-7.542023097870706</v>
+        <v>-11.30587170619768</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>12.52272795049702</v>
       </c>
       <c r="E22">
-        <v>-32.52846107883451</v>
+        <v>-37.28979374845328</v>
       </c>
       <c r="F22">
-        <v>0.6430059669297609</v>
+        <v>-1.515750962727057</v>
       </c>
       <c r="G22">
-        <v>-7.449006699853803</v>
+        <v>-11.30758987933256</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>12.5726369753981</v>
       </c>
       <c r="E23">
-        <v>-32.77429834728891</v>
+        <v>-37.92280648761548</v>
       </c>
       <c r="F23">
-        <v>0.8961484182860674</v>
+        <v>-1.360784959215742</v>
       </c>
       <c r="G23">
-        <v>-7.412779400017559</v>
+        <v>-11.10669935491851</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>12.55715194071493</v>
       </c>
       <c r="E24">
-        <v>-33.1707368115794</v>
+        <v>-38.06735537794032</v>
       </c>
       <c r="F24">
-        <v>0.8068454420598639</v>
+        <v>-1.203498698609186</v>
       </c>
       <c r="G24">
-        <v>-7.401314980815063</v>
+        <v>-11.01189857285594</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>12.4844965545231</v>
       </c>
       <c r="E25">
-        <v>-33.80499261685671</v>
+        <v>-37.95668173742986</v>
       </c>
       <c r="F25">
-        <v>1.069886883879624</v>
+        <v>-1.111325429332283</v>
       </c>
       <c r="G25">
-        <v>-7.101766888785188</v>
+        <v>-11.41167343108725</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>12.3613892361762</v>
       </c>
       <c r="E26">
-        <v>-33.93643157492934</v>
+        <v>-38.207679202016</v>
       </c>
       <c r="F26">
-        <v>0.9919159737237182</v>
+        <v>-1.246954852560048</v>
       </c>
       <c r="G26">
-        <v>-7.026624126134811</v>
+        <v>-11.34354902498012</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>12.19332005211547</v>
       </c>
       <c r="E27">
-        <v>-33.58022180948598</v>
+        <v>-37.91122265110386</v>
       </c>
       <c r="F27">
-        <v>0.9496907737334163</v>
+        <v>-1.042877430838959</v>
       </c>
       <c r="G27">
-        <v>-7.018301414649083</v>
+        <v>-11.45192635429924</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>11.98890785810776</v>
       </c>
       <c r="E28">
-        <v>-33.33331355692877</v>
+        <v>-38.08408129668765</v>
       </c>
       <c r="F28">
-        <v>1.096026845642366</v>
+        <v>-1.080452176229945</v>
       </c>
       <c r="G28">
-        <v>-7.163379451816564</v>
+        <v>-11.7547684391407</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>11.75290548349818</v>
       </c>
       <c r="E29">
-        <v>-33.74740854137517</v>
+        <v>-38.27527120505449</v>
       </c>
       <c r="F29">
-        <v>1.34263513492539</v>
+        <v>-1.068868286469197</v>
       </c>
       <c r="G29">
-        <v>-7.439793451618012</v>
+        <v>-11.30320340649303</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>11.48819301727852</v>
       </c>
       <c r="E30">
-        <v>-33.47356039694633</v>
+        <v>-38.50385272330266</v>
       </c>
       <c r="F30">
-        <v>1.201425000504964</v>
+        <v>-0.850787313803782</v>
       </c>
       <c r="G30">
-        <v>-7.245401528097547</v>
+        <v>-11.57837264117171</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>11.20297862446239</v>
       </c>
       <c r="E31">
-        <v>-32.7935987035096</v>
+        <v>-37.75025124979021</v>
       </c>
       <c r="F31">
-        <v>1.267901484579624</v>
+        <v>-0.9367039240873412</v>
       </c>
       <c r="G31">
-        <v>-7.2748686939426</v>
+        <v>-11.94601203385331</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>10.90154486704812</v>
       </c>
       <c r="E32">
-        <v>-32.72573499203065</v>
+        <v>-37.50109913836219</v>
       </c>
       <c r="F32">
-        <v>0.9493892479987972</v>
+        <v>-1.13249021647381</v>
       </c>
       <c r="G32">
-        <v>-7.659474632512969</v>
+        <v>-11.58089196632709</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>10.58784610484964</v>
       </c>
       <c r="E33">
-        <v>-33.12682193489002</v>
+        <v>-37.27976997123731</v>
       </c>
       <c r="F33">
-        <v>1.147803121786946</v>
+        <v>-1.134338304149455</v>
       </c>
       <c r="G33">
-        <v>-7.470071701120186</v>
+        <v>-11.88501523229224</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>10.26588303596367</v>
       </c>
       <c r="E34">
-        <v>-32.00819602127828</v>
+        <v>-36.84149067135294</v>
       </c>
       <c r="F34">
-        <v>1.088672599840312</v>
+        <v>-0.858806738630284</v>
       </c>
       <c r="G34">
-        <v>-8.25988179260627</v>
+        <v>-11.94604844985425</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>9.936456325401346</v>
       </c>
       <c r="E35">
-        <v>-31.40899513329435</v>
+        <v>-36.38733227736069</v>
       </c>
       <c r="F35">
-        <v>1.195982626668571</v>
+        <v>-1.138019568887497</v>
       </c>
       <c r="G35">
-        <v>-8.323222460409147</v>
+        <v>-12.22204863146328</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>9.605193904181398</v>
       </c>
       <c r="E36">
-        <v>-31.23948076576523</v>
+        <v>-36.1773967508391</v>
       </c>
       <c r="F36">
-        <v>1.198646656235974</v>
+        <v>-0.9790301849007846</v>
       </c>
       <c r="G36">
-        <v>-8.374529295176771</v>
+        <v>-12.18798973895526</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>9.276409121580786</v>
       </c>
       <c r="E37">
-        <v>-30.69474157043454</v>
+        <v>-35.7631840260685</v>
       </c>
       <c r="F37">
-        <v>1.189214864987699</v>
+        <v>-0.9315953823142765</v>
       </c>
       <c r="G37">
-        <v>-8.227772811420879</v>
+        <v>-11.97653857427093</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>8.950550128687761</v>
       </c>
       <c r="E38">
-        <v>-30.44221574587081</v>
+        <v>-35.19178796849167</v>
       </c>
       <c r="F38">
-        <v>1.197177132463408</v>
+        <v>-1.088078126540117</v>
       </c>
       <c r="G38">
-        <v>-8.101180860544687</v>
+        <v>-12.54282063094543</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>8.633592929888577</v>
       </c>
       <c r="E39">
-        <v>-30.19411876888659</v>
+        <v>-34.67532456486488</v>
       </c>
       <c r="F39">
-        <v>1.305545812832445</v>
+        <v>-1.060523313253394</v>
       </c>
       <c r="G39">
-        <v>-8.404592359218892</v>
+        <v>-12.36894415813182</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>8.328903573824942</v>
       </c>
       <c r="E40">
-        <v>-29.32846926300234</v>
+        <v>-34.02164160609467</v>
       </c>
       <c r="F40">
-        <v>1.377961691185178</v>
+        <v>-1.116128303533714</v>
       </c>
       <c r="G40">
-        <v>-8.687481786095155</v>
+        <v>-12.11079774861608</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>8.037160964166432</v>
       </c>
       <c r="E41">
-        <v>-28.86017523739514</v>
+        <v>-33.14892541652146</v>
       </c>
       <c r="F41">
-        <v>1.321243375115495</v>
+        <v>-0.8299107985184289</v>
       </c>
       <c r="G41">
-        <v>-8.59401846443045</v>
+        <v>-12.40993202245354</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>7.75851799831416</v>
       </c>
       <c r="E42">
-        <v>-28.14286948305417</v>
+        <v>-33.4429637623135</v>
       </c>
       <c r="F42">
-        <v>1.517357700993473</v>
+        <v>-0.8724226136300994</v>
       </c>
       <c r="G42">
-        <v>-8.517246913374752</v>
+        <v>-12.57217854878768</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>7.491485780375331</v>
       </c>
       <c r="E43">
-        <v>-27.49339121240008</v>
+        <v>-32.75512478834043</v>
       </c>
       <c r="F43">
-        <v>1.435158803613678</v>
+        <v>-0.7939911311982367</v>
       </c>
       <c r="G43">
-        <v>-8.592399607661747</v>
+        <v>-12.49469523044104</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>7.235248812543616</v>
       </c>
       <c r="E44">
-        <v>-27.30788227467586</v>
+        <v>-31.86780653432949</v>
       </c>
       <c r="F44">
-        <v>1.444002454005965</v>
+        <v>-0.6034715987587672</v>
       </c>
       <c r="G44">
-        <v>-8.903147275250976</v>
+        <v>-12.2465731528182</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.990348483646688</v>
       </c>
       <c r="E45">
-        <v>-26.45623933889734</v>
+        <v>-31.34300168158057</v>
       </c>
       <c r="F45">
-        <v>1.596559565109939</v>
+        <v>-0.7497132367837975</v>
       </c>
       <c r="G45">
-        <v>-8.782309052522038</v>
+        <v>-12.411825654502</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.755677570340868</v>
       </c>
       <c r="E46">
-        <v>-25.67113780018753</v>
+        <v>-30.89907990308265</v>
       </c>
       <c r="F46">
-        <v>1.805429092256223</v>
+        <v>-0.6487286234433154</v>
       </c>
       <c r="G46">
-        <v>-8.808382909189339</v>
+        <v>-12.71667061939471</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.531219076994356</v>
       </c>
       <c r="E47">
-        <v>-25.64572853253049</v>
+        <v>-30.34240365026775</v>
       </c>
       <c r="F47">
-        <v>1.603141772492584</v>
+        <v>-0.5839138443786709</v>
       </c>
       <c r="G47">
-        <v>-8.463165841445218</v>
+        <v>-12.38543729600847</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>6.319552683221125</v>
       </c>
       <c r="E48">
-        <v>-24.9280016301068</v>
+        <v>-29.89535269623053</v>
       </c>
       <c r="F48">
-        <v>1.68407161101129</v>
+        <v>-0.6433939373692865</v>
       </c>
       <c r="G48">
-        <v>-8.973916807243976</v>
+        <v>-12.57193356841778</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.120146518644474</v>
       </c>
       <c r="E49">
-        <v>-24.71797553410506</v>
+        <v>-29.74932752337919</v>
       </c>
       <c r="F49">
-        <v>1.833002129625807</v>
+        <v>-0.3896434643393252</v>
       </c>
       <c r="G49">
-        <v>-8.756082910759933</v>
+        <v>-12.82824593570477</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.931604540555708</v>
       </c>
       <c r="E50">
-        <v>-23.62592044173333</v>
+        <v>-29.1983209200219</v>
       </c>
       <c r="F50">
-        <v>1.796655024725771</v>
+        <v>-0.501590691888456</v>
       </c>
       <c r="G50">
-        <v>-8.817265102871202</v>
+        <v>-12.63366531108857</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.751483639087059</v>
       </c>
       <c r="E51">
-        <v>-23.33504749927265</v>
+        <v>-28.33615381064955</v>
       </c>
       <c r="F51">
-        <v>1.927601687025511</v>
+        <v>-0.5103664161537139</v>
       </c>
       <c r="G51">
-        <v>-9.172711756331672</v>
+        <v>-12.58275574178565</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>5.575469933404991</v>
       </c>
       <c r="E52">
-        <v>-22.52402044686892</v>
+        <v>-27.87389624089458</v>
       </c>
       <c r="F52">
-        <v>1.623713448573707</v>
+        <v>-0.4904665460362614</v>
       </c>
       <c r="G52">
-        <v>-8.922659630659441</v>
+        <v>-12.89819776294957</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>5.401352608236781</v>
       </c>
       <c r="E53">
-        <v>-22.14370561428274</v>
+        <v>-27.97736734349584</v>
       </c>
       <c r="F53">
-        <v>1.809534481104498</v>
+        <v>-0.4007659534567142</v>
       </c>
       <c r="G53">
-        <v>-9.126311150053247</v>
+        <v>-13.14765730097027</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>5.225620097501589</v>
       </c>
       <c r="E54">
-        <v>-21.58950190827603</v>
+        <v>-26.86207212251674</v>
       </c>
       <c r="F54">
-        <v>1.884331087372876</v>
+        <v>-0.4476664590684166</v>
       </c>
       <c r="G54">
-        <v>-9.01141866711284</v>
+        <v>-13.11389635756078</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>5.043132013040302</v>
       </c>
       <c r="E55">
-        <v>-21.28288799016469</v>
+        <v>-26.80531675777861</v>
       </c>
       <c r="F55">
-        <v>1.799125216320919</v>
+        <v>-0.5354352988646354</v>
       </c>
       <c r="G55">
-        <v>-9.151845387797646</v>
+        <v>-13.17979276651998</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>4.853798591822713</v>
       </c>
       <c r="E56">
-        <v>-20.51124054773167</v>
+        <v>-26.18125681172958</v>
       </c>
       <c r="F56">
-        <v>1.941944040237582</v>
+        <v>-0.3767283881622781</v>
       </c>
       <c r="G56">
-        <v>-8.912294312575982</v>
+        <v>-13.08060551161787</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>4.655620382324884</v>
       </c>
       <c r="E57">
-        <v>-20.19656141741266</v>
+        <v>-26.01553730541888</v>
       </c>
       <c r="F57">
-        <v>1.980569155495317</v>
+        <v>-0.4263782451838721</v>
       </c>
       <c r="G57">
-        <v>-9.309890831842452</v>
+        <v>-12.97685301441711</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>4.447376396173943</v>
       </c>
       <c r="E58">
-        <v>-20.31239072558085</v>
+        <v>-25.30450348757853</v>
       </c>
       <c r="F58">
-        <v>1.748303219424364</v>
+        <v>-0.5537662411211857</v>
       </c>
       <c r="G58">
-        <v>-9.28514781448194</v>
+        <v>-13.03089104925464</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>4.229102684945447</v>
       </c>
       <c r="E59">
-        <v>-19.75217320609195</v>
+        <v>-25.58310879395243</v>
       </c>
       <c r="F59">
-        <v>1.774976649794508</v>
+        <v>-0.3991117037533236</v>
       </c>
       <c r="G59">
-        <v>-9.452929572957743</v>
+        <v>-12.78482813095723</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>4.001399664026754</v>
       </c>
       <c r="E60">
-        <v>-19.38240971794364</v>
+        <v>-25.00311542847203</v>
       </c>
       <c r="F60">
-        <v>1.65949726363984</v>
+        <v>-0.5172973662129374</v>
       </c>
       <c r="G60">
-        <v>-9.356172258481463</v>
+        <v>-13.31676327766178</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>3.766043263565317</v>
       </c>
       <c r="E61">
-        <v>-18.91757997495231</v>
+        <v>-25.11870472751782</v>
       </c>
       <c r="F61">
-        <v>1.642586971479091</v>
+        <v>-0.5838724260085308</v>
       </c>
       <c r="G61">
-        <v>-9.474861937155413</v>
+        <v>-13.16925861061402</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>3.525048912690416</v>
       </c>
       <c r="E62">
-        <v>-18.39941386509864</v>
+        <v>-24.9342011110233</v>
       </c>
       <c r="F62">
-        <v>1.595177848282069</v>
+        <v>-0.4863901500470851</v>
       </c>
       <c r="G62">
-        <v>-9.329873284717493</v>
+        <v>-13.42246568618517</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>3.279672141209469</v>
       </c>
       <c r="E63">
-        <v>-18.9436685137105</v>
+        <v>-24.75975070682582</v>
       </c>
       <c r="F63">
-        <v>1.438685992014798</v>
+        <v>-0.7333471820066877</v>
       </c>
       <c r="G63">
-        <v>-9.616179194590282</v>
+        <v>-13.01679143580288</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>3.033011947214741</v>
       </c>
       <c r="E64">
-        <v>-18.45967879719272</v>
+        <v>-24.55489159966683</v>
       </c>
       <c r="F64">
-        <v>1.525646345225885</v>
+        <v>-0.5727366830126971</v>
       </c>
       <c r="G64">
-        <v>-9.443203190163363</v>
+        <v>-13.30803336907472</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.789186069701311</v>
       </c>
       <c r="E65">
-        <v>-18.4632698770808</v>
+        <v>-24.25834900774854</v>
       </c>
       <c r="F65">
-        <v>1.382983254380948</v>
+        <v>-0.8105816735415052</v>
       </c>
       <c r="G65">
-        <v>-9.520266069226517</v>
+        <v>-13.44789729701785</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>2.551481288676303</v>
       </c>
       <c r="E66">
-        <v>-18.02865411266864</v>
+        <v>-24.23103778100828</v>
       </c>
       <c r="F66">
-        <v>1.508910010219723</v>
+        <v>-0.8496027484177787</v>
       </c>
       <c r="G66">
-        <v>-9.330018948721222</v>
+        <v>-13.33267375952352</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>2.323017618798077</v>
       </c>
       <c r="E67">
-        <v>-18.11398414839518</v>
+        <v>-23.78161390659104</v>
       </c>
       <c r="F67">
-        <v>1.148391262642934</v>
+        <v>-0.9994519264820009</v>
       </c>
       <c r="G67">
-        <v>-9.459981034956391</v>
+        <v>-13.19005876823726</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>2.106573181654793</v>
       </c>
       <c r="E68">
-        <v>-18.13922586251393</v>
+        <v>-24.2002894424962</v>
       </c>
       <c r="F68">
-        <v>1.304112737225602</v>
+        <v>-1.118058399582237</v>
       </c>
       <c r="G68">
-        <v>-9.300717310153132</v>
+        <v>-12.75878737974532</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.904513014170151</v>
       </c>
       <c r="E69">
-        <v>-17.77951105818865</v>
+        <v>-24.01298270059094</v>
       </c>
       <c r="F69">
-        <v>0.9599045438099342</v>
+        <v>-1.052317505761263</v>
       </c>
       <c r="G69">
-        <v>-8.866353872127515</v>
+        <v>-13.03363880205223</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.719664260610859</v>
       </c>
       <c r="E70">
-        <v>-17.64252924793063</v>
+        <v>-24.08350009783838</v>
       </c>
       <c r="F70">
-        <v>1.004157587202289</v>
+        <v>-1.236354234906423</v>
       </c>
       <c r="G70">
-        <v>-9.093410948483969</v>
+        <v>-13.12695977025875</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.554105937017908</v>
       </c>
       <c r="E71">
-        <v>-17.37673499452442</v>
+        <v>-23.88873043076848</v>
       </c>
       <c r="F71">
-        <v>0.8025826634050577</v>
+        <v>-1.306427490244039</v>
       </c>
       <c r="G71">
-        <v>-9.216066660713967</v>
+        <v>-12.95843976012769</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.408819200440338</v>
       </c>
       <c r="E72">
-        <v>-17.9140339070605</v>
+        <v>-24.37241673952775</v>
       </c>
       <c r="F72">
-        <v>0.5870406368292235</v>
+        <v>-1.390664171434721</v>
       </c>
       <c r="G72">
-        <v>-9.232831263324837</v>
+        <v>-12.56217739071355</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.286605775655327</v>
       </c>
       <c r="E73">
-        <v>-17.63583616334729</v>
+        <v>-23.45399692603213</v>
       </c>
       <c r="F73">
-        <v>0.6469431971952669</v>
+        <v>-1.601110910115935</v>
       </c>
       <c r="G73">
-        <v>-8.875620089091937</v>
+        <v>-12.88868987616078</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.188500762014023</v>
       </c>
       <c r="E74">
-        <v>-17.53625954839262</v>
+        <v>-24.09747044015204</v>
       </c>
       <c r="F74">
-        <v>0.5168207604613122</v>
+        <v>-1.597921695615157</v>
       </c>
       <c r="G74">
-        <v>-8.654548479070485</v>
+        <v>-12.43587014675373</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.115308717526431</v>
       </c>
       <c r="E75">
-        <v>-17.82815592597904</v>
+        <v>-24.52639844121056</v>
       </c>
       <c r="F75">
-        <v>0.3709618281763752</v>
+        <v>-1.537581757260435</v>
       </c>
       <c r="G75">
-        <v>-8.716564928657652</v>
+        <v>-12.59784851889919</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.067644395292204</v>
       </c>
       <c r="E76">
-        <v>-18.37674432421624</v>
+        <v>-24.14342992285589</v>
       </c>
       <c r="F76">
-        <v>0.1759757387010108</v>
+        <v>-1.783461083228996</v>
       </c>
       <c r="G76">
-        <v>-8.293685773107768</v>
+        <v>-12.53675571151748</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.045148311261068</v>
       </c>
       <c r="E77">
-        <v>-18.5337646319582</v>
+        <v>-24.47326585567857</v>
       </c>
       <c r="F77">
-        <v>-0.03533415881392066</v>
+        <v>-1.867225595000082</v>
       </c>
       <c r="G77">
-        <v>-8.975694570198565</v>
+        <v>-12.22384294714557</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.048117686043171</v>
       </c>
       <c r="E78">
-        <v>-18.54936975338864</v>
+        <v>-24.90830276817344</v>
       </c>
       <c r="F78">
-        <v>0.04238409928413175</v>
+        <v>-1.904349708523944</v>
       </c>
       <c r="G78">
-        <v>-8.160476041698574</v>
+        <v>-12.2281532774377</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.076595442797156</v>
       </c>
       <c r="E79">
-        <v>-18.39061051162773</v>
+        <v>-25.0005568406577</v>
       </c>
       <c r="F79">
-        <v>-0.0476726912786193</v>
+        <v>-2.169298880472352</v>
       </c>
       <c r="G79">
-        <v>-8.437734230612536</v>
+        <v>-12.10216053530412</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.12992712995027</v>
       </c>
       <c r="E80">
-        <v>-19.58661672484553</v>
+        <v>-25.20086935991299</v>
       </c>
       <c r="F80">
-        <v>0.04712981613477012</v>
+        <v>-2.075055521055853</v>
       </c>
       <c r="G80">
-        <v>-7.72856240737202</v>
+        <v>-12.16976518576157</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.208217942783424</v>
       </c>
       <c r="E81">
-        <v>-19.67254904761509</v>
+        <v>-25.7113868771677</v>
       </c>
       <c r="F81">
-        <v>-0.07584132481081649</v>
+        <v>-2.160502447022024</v>
       </c>
       <c r="G81">
-        <v>-7.74995515264679</v>
+        <v>-11.61443772427653</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.311300149275034</v>
       </c>
       <c r="E82">
-        <v>-20.01353408344465</v>
+        <v>-25.99845137298794</v>
       </c>
       <c r="F82">
-        <v>0.046324643019249</v>
+        <v>-2.052471740553329</v>
       </c>
       <c r="G82">
-        <v>-7.892139773012948</v>
+        <v>-12.22094621979871</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.438665954147462</v>
       </c>
       <c r="E83">
-        <v>-20.54760419401326</v>
+        <v>-26.24058434970406</v>
       </c>
       <c r="F83">
-        <v>-0.1579325344282475</v>
+        <v>-2.33787993061608</v>
       </c>
       <c r="G83">
-        <v>-7.754060229115487</v>
+        <v>-11.95757576942199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.589928447935234</v>
       </c>
       <c r="E84">
-        <v>-21.47240009891168</v>
+        <v>-27.20153106260572</v>
       </c>
       <c r="F84">
-        <v>-0.4638568999561329</v>
+        <v>-2.243434449553297</v>
       </c>
       <c r="G84">
-        <v>-7.575330496541313</v>
+        <v>-11.87707654408907</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.763828929589557</v>
       </c>
       <c r="E85">
-        <v>-22.29101234527825</v>
+        <v>-27.92740468976921</v>
       </c>
       <c r="F85">
-        <v>-0.1266069927239814</v>
+        <v>-2.280993455963629</v>
       </c>
       <c r="G85">
-        <v>-7.413722905496251</v>
+        <v>-11.58437466023441</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.95895063173855</v>
       </c>
       <c r="E86">
-        <v>-22.79266763889996</v>
+        <v>-28.24400842154148</v>
       </c>
       <c r="F86">
-        <v>-0.3307250044478076</v>
+        <v>-2.535043797993404</v>
       </c>
       <c r="G86">
-        <v>-7.255204053439329</v>
+        <v>-11.73791445180026</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.175088842317405</v>
       </c>
       <c r="E87">
-        <v>-24.75827442429932</v>
+        <v>-29.74552586944975</v>
       </c>
       <c r="F87">
-        <v>-0.3071049363243825</v>
+        <v>-2.511456864566091</v>
       </c>
       <c r="G87">
-        <v>-7.567438155975691</v>
+        <v>-11.7208717633641</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.410843344096493</v>
       </c>
       <c r="E88">
-        <v>-25.02750578947734</v>
+        <v>-30.16335458071548</v>
       </c>
       <c r="F88">
-        <v>-0.4305863515900936</v>
+        <v>-2.446437478752955</v>
       </c>
       <c r="G88">
-        <v>-7.269674447991483</v>
+        <v>-11.25311816302939</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.664455824454343</v>
       </c>
       <c r="E89">
-        <v>-26.83738288222693</v>
+        <v>-30.80937536146471</v>
       </c>
       <c r="F89">
-        <v>-0.4848427597386556</v>
+        <v>-2.703839395294457</v>
       </c>
       <c r="G89">
-        <v>-7.127612317810279</v>
+        <v>-11.40637324767887</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.933663547212363</v>
       </c>
       <c r="E90">
-        <v>-27.41148470302334</v>
+        <v>-32.19312078585551</v>
       </c>
       <c r="F90">
-        <v>-0.5759532336377676</v>
+        <v>-2.81777884644732</v>
       </c>
       <c r="G90">
-        <v>-7.345267444835201</v>
+        <v>-11.7060603826214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.214748057185266</v>
       </c>
       <c r="E91">
-        <v>-29.14505248026967</v>
+        <v>-33.33770617671621</v>
       </c>
       <c r="F91">
-        <v>-0.7380829584484925</v>
+        <v>-2.772091899080719</v>
       </c>
       <c r="G91">
-        <v>-7.317965375772832</v>
+        <v>-11.44481530248089</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.50237068315584</v>
       </c>
       <c r="E92">
-        <v>-30.11607051936438</v>
+        <v>-34.53816614412056</v>
       </c>
       <c r="F92">
-        <v>-0.9401035439084303</v>
+        <v>-2.880317271889071</v>
       </c>
       <c r="G92">
-        <v>-7.438747319227602</v>
+        <v>-12.05249242057843</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.789604600694125</v>
       </c>
       <c r="E93">
-        <v>-31.44956346769207</v>
+        <v>-35.56312057288363</v>
       </c>
       <c r="F93">
-        <v>-1.1003528747148</v>
+        <v>-3.131709382923263</v>
       </c>
       <c r="G93">
-        <v>-7.579316393370596</v>
+        <v>-12.18321593228763</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.066097180555149</v>
       </c>
       <c r="E94">
-        <v>-33.25234217743462</v>
+        <v>-36.76859808948848</v>
       </c>
       <c r="F94">
-        <v>-0.9730883055205038</v>
+        <v>-3.210099446984986</v>
       </c>
       <c r="G94">
-        <v>-8.07678213992026</v>
+        <v>-11.99447842054824</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.324562972701017</v>
       </c>
       <c r="E95">
-        <v>-35.11325970072465</v>
+        <v>-38.27514667201928</v>
       </c>
       <c r="F95">
-        <v>-1.158872061518168</v>
+        <v>-3.270839486795259</v>
       </c>
       <c r="G95">
-        <v>-8.164955209813208</v>
+        <v>-11.90767260596301</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.555066184871183</v>
       </c>
       <c r="E96">
-        <v>-36.67550172083879</v>
+        <v>-40.05172589539046</v>
       </c>
       <c r="F96">
-        <v>-1.345022784275273</v>
+        <v>-3.518937180668517</v>
       </c>
       <c r="G96">
-        <v>-8.211594175370461</v>
+        <v>-12.21757939498527</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.7492768488727</v>
       </c>
       <c r="E97">
-        <v>-38.36631843921571</v>
+        <v>-41.6168638746325</v>
       </c>
       <c r="F97">
-        <v>-1.455221328237094</v>
+        <v>-3.815123259009091</v>
       </c>
       <c r="G97">
-        <v>-8.746538607970214</v>
+        <v>-12.90258092524357</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.897546998407148</v>
       </c>
       <c r="E98">
-        <v>-39.99041488580061</v>
+        <v>-43.1032788617252</v>
       </c>
       <c r="F98">
-        <v>-1.684625254931376</v>
+        <v>-3.76463095233885</v>
       </c>
       <c r="G98">
-        <v>-8.554801741972245</v>
+        <v>-12.74273123387986</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.995940529779901</v>
       </c>
       <c r="E99">
-        <v>-41.85985046869907</v>
+        <v>-44.78006183915235</v>
       </c>
       <c r="F99">
-        <v>-1.898740004472186</v>
+        <v>-3.92524724990466</v>
       </c>
       <c r="G99">
-        <v>-8.717935494510911</v>
+        <v>-13.28228394587027</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>5.033387613645999</v>
       </c>
       <c r="E100">
-        <v>-44.18004356161003</v>
+        <v>-46.44034985000656</v>
       </c>
       <c r="F100">
-        <v>-2.062471791839925</v>
+        <v>-4.299634524539119</v>
       </c>
       <c r="G100">
-        <v>-9.025111083463266</v>
+        <v>-13.68605463256749</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>5.012618924671136</v>
       </c>
       <c r="E101">
-        <v>-46.21291856415633</v>
+        <v>-48.19233040256807</v>
       </c>
       <c r="F101">
-        <v>-2.182133605011328</v>
+        <v>-4.341469563482702</v>
       </c>
       <c r="G101">
-        <v>-9.378892532517481</v>
+        <v>-13.51267474158477</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>4.915082242974677</v>
       </c>
       <c r="E102">
-        <v>-48.52339355184682</v>
+        <v>-50.4505739710541</v>
       </c>
       <c r="F102">
-        <v>-2.299807336416011</v>
+        <v>-4.373247393788898</v>
       </c>
       <c r="G102">
-        <v>-9.525493420633028</v>
+        <v>-13.65212485133549</v>
       </c>
     </row>
   </sheetData>
